--- a/Autogen/UniversalDataBlock.xlsx
+++ b/Autogen/UniversalDataBlock.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="40">
   <si>
     <t xml:space="preserve">Member ID</t>
   </si>
@@ -43,51 +43,78 @@
     <t xml:space="preserve">Default</t>
   </si>
   <si>
+    <t xml:space="preserve">NVM Storage</t>
+  </si>
+  <si>
     <t xml:space="preserve">Description</t>
   </si>
   <si>
     <t xml:space="preserve">Atams Version Number</t>
   </si>
   <si>
+    <t xml:space="preserve">float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal Unlock</t>
+  </si>
+  <si>
     <t xml:space="preserve">uint32_t</t>
   </si>
   <si>
-    <t xml:space="preserve">RO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOGEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memory Map Gen Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memory Map Gen Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memory Map Checksum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universal Unlock</t>
-  </si>
-  <si>
     <t xml:space="preserve">RW</t>
   </si>
   <si>
+    <t xml:space="preserve">Map Gen Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint8_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint16_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Minute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Number Of Blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Checksum</t>
+  </si>
+  <si>
     <t xml:space="preserve">Node ID</t>
   </si>
   <si>
-    <t xml:space="preserve">uint8_t</t>
-  </si>
-  <si>
     <t xml:space="preserve">0</t>
   </si>
   <si>
     <t xml:space="preserve">NODE_ID_MAX</t>
   </si>
   <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
     <t xml:space="preserve">First Node ID</t>
   </si>
   <si>
@@ -100,10 +127,19 @@
     <t xml:space="preserve">Watchdog Timeout</t>
   </si>
   <si>
+    <t xml:space="preserve">Watchdog Fault Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watchdog Reset</t>
+  </si>
+  <si>
     <t xml:space="preserve">Store NVM</t>
   </si>
   <si>
     <t xml:space="preserve">Restore Factory NVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVM Status</t>
   </si>
 </sst>
 </file>
@@ -192,7 +228,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -202,6 +238,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -388,17 +428,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="54.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="28.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="54.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -426,284 +467,537 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>11</v>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H21" type="list">
+      <formula1>"NO,YES"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/Autogen/UniversalDataBlock.xlsx
+++ b/Autogen/UniversalDataBlock.xlsx
@@ -97,9 +97,6 @@
     <t xml:space="preserve">Map Gen Second</t>
   </si>
   <si>
-    <t xml:space="preserve">Map Number Of Blocks</t>
-  </si>
-  <si>
     <t xml:space="preserve">Map Checksum</t>
   </si>
   <si>
@@ -125,6 +122,9 @@
   </si>
   <si>
     <t xml:space="preserve">Watchdog Timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watchdog Counter</t>
   </si>
   <si>
     <t xml:space="preserve">Watchdog Fault Active</t>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -710,30 +710,30 @@
         <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -745,16 +745,16 @@
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -771,16 +771,16 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -797,16 +797,16 @@
         <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -814,7 +814,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>16</v>
@@ -823,16 +823,16 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -843,7 +843,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -855,10 +855,10 @@
         <v>12</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Autogen/UniversalDataBlock.xlsx
+++ b/Autogen/UniversalDataBlock.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="43">
   <si>
     <t xml:space="preserve">Member ID</t>
   </si>
@@ -131,6 +131,15 @@
   </si>
   <si>
     <t xml:space="preserve">Watchdog Reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRC Error Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uin32_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBS Error Count</t>
   </si>
   <si>
     <t xml:space="preserve">Store NVM</t>
@@ -428,7 +437,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.6"/>
@@ -918,10 +927,10 @@
         <v>37</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>12</v>
@@ -941,13 +950,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>12</v>
@@ -967,33 +976,85 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="C23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H23" type="list">
       <formula1>"NO,YES"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Autogen/UniversalDataBlock.xlsx
+++ b/Autogen/UniversalDataBlock.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="42">
   <si>
     <t xml:space="preserve">Member ID</t>
   </si>
@@ -49,10 +49,10 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Atams Version Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">float</t>
+    <t xml:space="preserve">Atams Version Major</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint8_t</t>
   </si>
   <si>
     <t xml:space="preserve">RO</t>
@@ -64,7 +64,10 @@
     <t xml:space="preserve">NO</t>
   </si>
   <si>
-    <t xml:space="preserve">Universal Unlock</t>
+    <t xml:space="preserve">Atams Version Minor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal Write Unlock</t>
   </si>
   <si>
     <t xml:space="preserve">uint32_t</t>
@@ -79,9 +82,6 @@
     <t xml:space="preserve">Map Gen Month</t>
   </si>
   <si>
-    <t xml:space="preserve">uint8_t</t>
-  </si>
-  <si>
     <t xml:space="preserve">Map Gen Year</t>
   </si>
   <si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NODE_ID_MAX</t>
   </si>
   <si>
     <t xml:space="preserve">YES</t>
@@ -437,7 +434,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.6"/>
@@ -511,10 +508,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>12</v>
@@ -534,13 +531,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
@@ -563,7 +560,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -586,10 +583,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
@@ -612,10 +609,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
@@ -638,10 +635,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
@@ -664,10 +661,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -690,10 +687,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -716,117 +713,117 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>12</v>
@@ -841,18 +838,18 @@
         <v>27</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -864,18 +861,18 @@
         <v>12</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>11</v>
@@ -898,13 +895,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>12</v>
@@ -924,13 +921,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>12</v>
@@ -950,10 +947,10 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>11</v>
@@ -976,13 +973,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>12</v>
@@ -1002,13 +999,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>12</v>
@@ -1028,13 +1025,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>12</v>
@@ -1049,12 +1046,38 @@
         <v>12</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H23" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H24" type="list">
       <formula1>"NO,YES"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Autogen/UniversalDataBlock.xlsx
+++ b/Autogen/UniversalDataBlock.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="46">
   <si>
     <t xml:space="preserve">Member ID</t>
   </si>
@@ -61,69 +61,93 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">NO</t>
+    <t xml:space="preserve">true</t>
   </si>
   <si>
     <t xml:space="preserve">Atams Version Minor</t>
   </si>
   <si>
-    <t xml:space="preserve">Universal Write Unlock</t>
+    <t xml:space="preserve">Map Gen Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint16_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Minute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Checksum</t>
   </si>
   <si>
     <t xml:space="preserve">uint32_t</t>
   </si>
   <si>
+    <t xml:space="preserve">Universal Unlock</t>
+  </si>
+  <si>
     <t xml:space="preserve">RW</t>
   </si>
   <si>
-    <t xml:space="preserve">Map Gen Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uint16_t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Hour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Minute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Second</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Checksum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Node ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Node ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Node ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Previous Node ID</t>
+    <t xml:space="preserve">false</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node ID Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Node ID Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Node ID Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Node ID Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node ID Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Node ID Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Node ID Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Node ID Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply Identifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore User Blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restore All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage Process Complete</t>
   </si>
   <si>
     <t xml:space="preserve">Watchdog Timeout</t>
   </si>
   <si>
-    <t xml:space="preserve">Watchdog Counter</t>
-  </si>
-  <si>
     <t xml:space="preserve">Watchdog Fault Active</t>
   </si>
   <si>
@@ -133,19 +157,7 @@
     <t xml:space="preserve">CRC Error Count</t>
   </si>
   <si>
-    <t xml:space="preserve">uin32_t</t>
-  </si>
-  <si>
     <t xml:space="preserve">COBS Error Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store NVM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restore Factory NVM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVM Status</t>
   </si>
 </sst>
 </file>
@@ -180,7 +192,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -234,7 +246,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -249,6 +261,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -434,12 +450,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.29"/>
@@ -448,7 +464,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="54.58"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -481,7 +497,7 @@
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -507,7 +523,7 @@
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -533,11 +549,11 @@
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
@@ -557,10 +573,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -583,10 +599,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
@@ -609,10 +625,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
@@ -635,10 +651,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
@@ -661,9 +677,9 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -687,10 +703,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -713,14 +729,14 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
@@ -734,18 +750,18 @@
         <v>12</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>12</v>
@@ -757,21 +773,21 @@
         <v>12</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
@@ -783,21 +799,21 @@
         <v>12</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>12</v>
@@ -809,21 +825,21 @@
         <v>12</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>12</v>
@@ -835,21 +851,21 @@
         <v>12</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -861,18 +877,18 @@
         <v>12</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>11</v>
@@ -895,9 +911,9 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -921,13 +937,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>12</v>
@@ -947,13 +963,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>12</v>
@@ -968,18 +984,18 @@
         <v>12</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>12</v>
@@ -994,18 +1010,18 @@
         <v>12</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>12</v>
@@ -1020,18 +1036,18 @@
         <v>12</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>12</v>
@@ -1046,39 +1062,229 @@
         <v>12</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="B26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H24" type="list">
-      <formula1>"NO,YES"</formula1>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H24 H26:H30" type="list">
+      <formula1>"true,false"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B30" type="list">
+      <formula1>"uint8_t,int8_t,uint16_t,int16_t,uint32_t,int32_t,float"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/Autogen/UniversalDataBlock.xlsx
+++ b/Autogen/UniversalDataBlock.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="47">
   <si>
     <t xml:space="preserve">Member ID</t>
   </si>
@@ -61,91 +61,94 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
+    <t xml:space="preserve">false</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atams Version Minor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint16_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Minute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Gen Second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Checksum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint32_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuration Passkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCESS_KEY, APPLY_KEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuration Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENIED, APPLIED, CANCELLED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node ID</t>
+  </si>
+  <si>
     <t xml:space="preserve">true</t>
   </si>
   <si>
-    <t xml:space="preserve">Atams Version Minor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uint16_t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Hour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Minute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Gen Second</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map Checksum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uint32_t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universal Unlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">false</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Node ID Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Node ID Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Node ID Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Previous Node ID Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Node ID Display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Node ID Display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Node ID Display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Previous Node ID Display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apply Identifiers</t>
+    <t xml:space="preserve">First Node ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Node ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Node ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watchdog Period</t>
   </si>
   <si>
     <t xml:space="preserve">Store All</t>
   </si>
   <si>
+    <t xml:space="preserve">Passcode</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restore User Blocks</t>
   </si>
   <si>
     <t xml:space="preserve">Restore All</t>
   </si>
   <si>
+    <t xml:space="preserve">Reset Node</t>
+  </si>
+  <si>
     <t xml:space="preserve">Storage Status</t>
   </si>
   <si>
     <t xml:space="preserve">Storage Process Complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watchdog Timeout</t>
   </si>
   <si>
     <t xml:space="preserve">Watchdog Fault Active</t>
@@ -450,7 +453,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.6"/>
@@ -732,7 +735,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
@@ -750,6 +753,9 @@
         <v>12</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -761,7 +767,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>12</v>
@@ -776,12 +782,15 @@
         <v>12</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>10</v>
@@ -802,12 +811,12 @@
         <v>12</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>10</v>
@@ -828,12 +837,12 @@
         <v>12</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>10</v>
@@ -854,18 +863,18 @@
         <v>12</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -880,18 +889,18 @@
         <v>12</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>12</v>
@@ -906,18 +915,18 @@
         <v>12</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>12</v>
@@ -932,18 +941,18 @@
         <v>12</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>12</v>
@@ -959,11 +968,14 @@
       </c>
       <c r="H19" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>23</v>
@@ -984,12 +996,15 @@
         <v>12</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>23</v>
@@ -1010,12 +1025,15 @@
         <v>12</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>23</v>
@@ -1036,18 +1054,21 @@
         <v>12</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>12</v>
@@ -1062,12 +1083,12 @@
         <v>12</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>10</v>
@@ -1087,13 +1108,13 @@
       <c r="G24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>26</v>
+      <c r="H24" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>10</v>
@@ -1113,13 +1134,13 @@
       <c r="G25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>26</v>
+      <c r="H25" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>23</v>
@@ -1142,13 +1163,16 @@
       <c r="H26" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="I26" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>11</v>
@@ -1166,18 +1190,18 @@
         <v>12</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>12</v>
@@ -1192,60 +1216,58 @@
         <v>12</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
@@ -1257,33 +1279,33 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H24 H26:H30" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H23 H25:H28" type="list">
       <formula1>"true,false"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B30" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B28" type="list">
       <formula1>"uint8_t,int8_t,uint16_t,int16_t,uint32_t,int32_t,float"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Autogen/UniversalDataBlock.xlsx
+++ b/Autogen/UniversalDataBlock.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="48">
   <si>
     <t xml:space="preserve">Member ID</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve">Map Gen Second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Number of Vars</t>
   </si>
   <si>
     <t xml:space="preserve">Map Checksum</t>
@@ -453,7 +456,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.6"/>
@@ -709,7 +712,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -732,13 +735,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
@@ -754,90 +757,90 @@
       </c>
       <c r="H11" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -848,7 +851,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>12</v>
@@ -863,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -874,7 +877,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -889,7 +892,7 @@
         <v>12</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -900,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>12</v>
@@ -915,7 +918,7 @@
         <v>12</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -923,10 +926,10 @@
         <v>35</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>12</v>
@@ -941,7 +944,7 @@
         <v>12</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -949,10 +952,10 @@
         <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>12</v>
@@ -967,39 +970,36 @@
         <v>12</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1007,10 +1007,10 @@
         <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>12</v>
@@ -1028,7 +1028,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1036,10 +1036,10 @@
         <v>40</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>12</v>
@@ -1057,7 +1057,7 @@
         <v>13</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1065,10 +1065,10 @@
         <v>41</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>12</v>
@@ -1084,6 +1084,9 @@
       </c>
       <c r="H23" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1108,7 +1111,7 @@
       <c r="G24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1134,7 +1137,7 @@
       <c r="G25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1143,10 +1146,10 @@
         <v>44</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>12</v>
@@ -1162,9 +1165,6 @@
       </c>
       <c r="H26" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1172,10 +1172,10 @@
         <v>45</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>12</v>
@@ -1191,6 +1191,9 @@
       </c>
       <c r="H27" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1198,7 +1201,7 @@
         <v>46</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>11</v>
@@ -1220,14 +1223,30 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="A29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
@@ -1279,15 +1298,15 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4"/>
@@ -1299,13 +1318,23 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H23 H25:H28" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H24 H26:H29" type="list">
       <formula1>"true,false"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B28" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B29" type="list">
       <formula1>"uint8_t,int8_t,uint16_t,int16_t,uint32_t,int32_t,float"</formula1>
       <formula2>0</formula2>
     </dataValidation>
